--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486987_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486987_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5115</v>
+        <v>3.1839</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3313</v>
+        <v>1.6262</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1801</v>
+        <v>1.5577</v>
       </c>
       <c r="G2" t="n">
         <v>0.1643</v>
@@ -610,13 +610,13 @@
         <v>3.4908</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5185</v>
+        <v>0.1909</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5456</v>
+        <v>0.8405</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0271</v>
+        <v>-0.6496</v>
       </c>
       <c r="V2" t="n">
         <v>2.8287</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8746</v>
+        <v>2.7315</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2367</v>
+        <v>1.8635</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3621</v>
+        <v>0.868</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6576</v>
+        <v>1.1213</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4946</v>
+        <v>3.6206</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1629</v>
+        <v>-2.4994</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9726</v>
+        <v>1.8249</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8809</v>
+        <v>4.5618</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0916</v>
+        <v>-2.7369</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6850000000000001</v>
+        <v>-0.7037</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3863</v>
+        <v>-0.9412</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0713</v>
+        <v>0.2375</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0267</v>
+        <v>2.8748</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.399</v>
+        <v>-0.6353</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3176</v>
+        <v>0.55</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7166</v>
+        <v>-1.1853</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1786</v>
+        <v>0.6028</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>0.7207</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3573</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6164</v>
+        <v>2.0368</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1042</v>
+        <v>4.1321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5123</v>
+        <v>-2.0954</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1213</v>
+        <v>4.6576</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6206</v>
+        <v>2.4946</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4994</v>
+        <v>2.1629</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8249</v>
+        <v>3.9726</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5618</v>
+        <v>2.8809</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.7369</v>
+        <v>1.0916</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7037</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9412</v>
+        <v>-0.3863</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2375</v>
+        <v>1.0713</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6427</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8748</v>
+        <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7504</v>
+        <v>-1.2368</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2094</v>
+        <v>0.213</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.541</v>
+        <v>-1.4498</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6028</v>
+        <v>-1.1786</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1179</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8348</v>
+        <v>-0.2565</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8722</v>
+        <v>0.7216</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0374</v>
+        <v>-0.9781</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7427</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2366</v>
+        <v>0.1453</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8286</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.592</v>
+        <v>-0.5327</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4805</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2109</v>
+        <v>-0.4076</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1125</v>
+        <v>0.9992</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3234</v>
+        <v>-1.4068</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6293</v>
+        <v>1.1716</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0477</v>
+        <v>0.0558</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4184</v>
+        <v>1.1158</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6584</v>
+        <v>3.2853</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6584</v>
+        <v>1.2468</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.0385</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0291</v>
+        <v>-2.1137</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3893</v>
+        <v>-1.191</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4184</v>
+        <v>-0.9227</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.4641</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.0801</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4184</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7709</v>
+        <v>0.178</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3525</v>
+        <v>-1.0767</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2965</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6672</v>
+        <v>-0.6293</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9827</v>
+        <v>-0.3059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3156</v>
+        <v>-0.3234</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2634</v>
+        <v>-0.6293</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4216</v>
+        <v>-1.0477</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8418</v>
+        <v>0.4184</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5216</v>
+        <v>-0.6584</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5611</v>
+        <v>-0.6584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7418</v>
+        <v>0.0291</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1395</v>
+        <v>-0.3893</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8813</v>
+        <v>0.4184</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5963000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5656</v>
+        <v>0.3525</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0307</v>
+        <v>-0.3525</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3343</v>
+        <v>-0.6968</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2832</v>
+        <v>-0.9827</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0511</v>
+        <v>0.2859</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1716</v>
+        <v>-1.2634</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0558</v>
+        <v>-0.4216</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1158</v>
+        <v>-0.8418</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2853</v>
+        <v>-0.5216</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2468</v>
+        <v>-0.5611</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0385</v>
+        <v>0.0395</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1137</v>
+        <v>-0.7418</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.191</v>
+        <v>0.1395</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9227</v>
+        <v>-0.8813</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4641</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0801</v>
+        <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8254</v>
+        <v>0.5666</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1044</v>
+        <v>0.5656</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.721</v>
+        <v>0.001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2965</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5397</v>
+        <v>-1.9351</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0455</v>
+        <v>-0.5303</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4942</v>
+        <v>-1.4047</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2703</v>
+        <v>-4.0129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0554</v>
+        <v>-1.1453</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3257</v>
+        <v>-2.8676</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9307</v>
+        <v>-1.7406</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4702</v>
+        <v>-0.4248</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5395</v>
+        <v>-1.3158</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.201</v>
+        <v>-2.2723</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4148</v>
+        <v>-0.7204</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2138</v>
+        <v>-1.5518</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4641</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
         <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9729</v>
+        <v>-0.215</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4879</v>
+        <v>0.0851</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4608</v>
+        <v>-0.3001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2965</v>
+        <v>1.0608</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2965</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0675</v>
+        <v>-2.3504</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6035</v>
+        <v>-1.1229</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.464</v>
+        <v>-1.2274</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0129</v>
+        <v>-0.2703</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1453</v>
+        <v>0.0554</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8676</v>
+        <v>-0.3257</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7406</v>
+        <v>0.9307</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4248</v>
+        <v>1.4702</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3158</v>
+        <v>-0.5395</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2723</v>
+        <v>-1.201</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7204</v>
+        <v>-1.4148</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5518</v>
+        <v>0.2138</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2321</v>
+        <v>-2.4641</v>
       </c>
       <c r="R10" t="n">
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3475</v>
+        <v>-0.7836</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9881</v>
+        <v>0.4105</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3594</v>
+        <v>-1.194</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0608</v>
+        <v>-1.2965</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2965</v>
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0177</v>
+        <v>1.6765</v>
       </c>
       <c r="E11" t="n">
-        <v>5.741999999999999</v>
+        <v>6.400799999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.7242</v>
+        <v>-4.724200000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1961999999999993</v>
+        <v>0.1961999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7059</v>
+        <v>4.705900000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.5099</v>
+        <v>-4.509900000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>9.370000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>10.6611</v>
@@ -1312,16 +1312,16 @@
         <v>17.454</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.5254</v>
+        <v>-2.8666</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2143</v>
+        <v>3.8731</v>
       </c>
       <c r="U11" t="n">
         <v>-6.7397</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2402</v>
+        <v>0.2401999999999997</v>
       </c>
       <c r="W11" t="n">
         <v>6.505000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.1731</v>
+        <v>11.7198</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9665</v>
+        <v>10.2343</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2066</v>
+        <v>1.4855</v>
       </c>
       <c r="G12" t="n">
         <v>7.3333</v>
@@ -1390,13 +1390,13 @@
         <v>2.4641</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4024</v>
+        <v>0.9492</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6773</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2749</v>
+        <v>0.0041</v>
       </c>
       <c r="V12" t="n">
         <v>1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.039</v>
+        <v>6.9308</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8184</v>
+        <v>5.6092</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2206</v>
+        <v>1.3217</v>
       </c>
       <c r="G13" t="n">
         <v>3.2071</v>
@@ -1468,13 +1468,13 @@
         <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1871</v>
+        <v>1.079</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2512</v>
+        <v>1.042</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0641</v>
+        <v>0.037</v>
       </c>
       <c r="V13" t="n">
         <v>3.0554</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8356</v>
+        <v>2.5783</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4896</v>
+        <v>1.8009</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3461</v>
+        <v>0.7774</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7109</v>
+        <v>2.1498</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8691</v>
+        <v>-1.0415</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8418</v>
+        <v>3.1914</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8307</v>
+        <v>2.4519</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1996</v>
+        <v>0.0973</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6311</v>
+        <v>2.3545</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1198</v>
+        <v>-0.302</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3305</v>
+        <v>-1.1389</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2107</v>
+        <v>0.8368</v>
       </c>
       <c r="P14" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1596</v>
+        <v>0.1143</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8909</v>
+        <v>0.3757</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2687</v>
+        <v>-0.2615</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2402</v>
+        <v>0.1088</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4004</v>
+        <v>2.4189</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8009</v>
+        <v>2.2804</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5996</v>
+        <v>0.1386</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1498</v>
+        <v>1.7109</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0415</v>
+        <v>0.8691</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1914</v>
+        <v>0.8418</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4519</v>
+        <v>2.8307</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0973</v>
+        <v>2.1996</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3545</v>
+        <v>0.6311</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.302</v>
+        <v>-1.1198</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1389</v>
+        <v>-1.3305</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8368</v>
+        <v>0.2107</v>
       </c>
       <c r="P15" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0636</v>
+        <v>0.7429</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3757</v>
+        <v>0.6817</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4393</v>
+        <v>0.0612</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1088</v>
+        <v>-0.2402</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1088</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5165</v>
+        <v>-0.3438</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.5073</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3376</v>
+        <v>-0.8511</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2513</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7348</v>
+        <v>0.9075</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1776</v>
+        <v>0.8638</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4427</v>
+        <v>0.0437</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5893</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0324</v>
+        <v>-1.573</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5289</v>
+        <v>-1.584</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5613</v>
+        <v>0.011</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8317</v>
+        <v>-0.0911</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0738</v>
+        <v>-0.649</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2422</v>
+        <v>0.5579</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5795</v>
+        <v>0.4423</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6584</v>
+        <v>-0.347</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0789</v>
+        <v>0.7893</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2522</v>
+        <v>-0.5335</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4154</v>
+        <v>-0.302</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1632</v>
+        <v>-0.2314</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3188</v>
+        <v>-0.2499</v>
       </c>
       <c r="T17" t="n">
-        <v>1.476</v>
+        <v>0.027</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1572</v>
+        <v>-0.2769</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0674</v>
+        <v>-1.8378</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3748</v>
+        <v>0.9013</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3074</v>
+        <v>-2.7392</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0911</v>
+        <v>-0.8317</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.649</v>
+        <v>-1.0738</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5579</v>
+        <v>0.2422</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4423</v>
+        <v>-0.5795</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.347</v>
+        <v>-0.6584</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7893</v>
+        <v>0.0789</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5335</v>
+        <v>-0.2522</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.302</v>
+        <v>-0.4154</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2314</v>
+        <v>0.1632</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2321</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2558</v>
+        <v>0.5134</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2362</v>
+        <v>0.8484</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0195</v>
+        <v>-0.3351</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0109</v>
+        <v>-2.7748</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8115</v>
+        <v>-2.7655</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1993</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-3.4557</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6249</v>
+        <v>0.6111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4534</v>
+        <v>0.5927</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1715</v>
+        <v>0.0185</v>
       </c>
       <c r="V19" t="n">
         <v>0.4805</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3297</v>
+        <v>-5.3157</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0806</v>
+        <v>-4.1852</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2491</v>
+        <v>-1.1306</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3565</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.045</v>
+        <v>-0.031</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5733</v>
+        <v>0.4687</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6183</v>
+        <v>-0.4997</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5541</v>
+        <v>-5.6335</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.194</v>
+        <v>-3.671</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3601</v>
+        <v>-1.9626</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4966</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3162</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1858</v>
+        <v>0.7088</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.502</v>
+        <v>-0.1045</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3573</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.955</v>
+        <v>-5.7921</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2401</v>
+        <v>-4.4033</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7149</v>
+        <v>-1.3888</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1142</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4835</v>
+        <v>-0.3206</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.651</v>
+        <v>0.1858</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8325</v>
+        <v>-0.5064</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.017899999999997</v>
+        <v>0.3770999999999951</v>
       </c>
       <c r="E23" t="n">
-        <v>4.724400000000001</v>
+        <v>4.724399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.742000000000001</v>
+        <v>-4.3474</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1960000000000006</v>
@@ -2248,13 +2248,13 @@
         <v>13.3472</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5253</v>
+        <v>4.9202</v>
       </c>
       <c r="T23" t="n">
-        <v>6.7396</v>
+        <v>6.739700000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.2143</v>
+        <v>-1.8196</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2403000000000006</v>
